--- a/frontend/playwright/fixtures/quantstudio-e2e-results-demo.xlsx
+++ b/frontend/playwright/fixtures/quantstudio-e2e-results-demo.xlsx
@@ -442,7 +442,7 @@
         <v>A1</v>
       </c>
       <c r="C2" t="str">
-        <v>DEMO-QS7-2026-00001</v>
+        <v>DEV01262000000000101</v>
       </c>
       <c r="D2" t="str">
         <v>VIH-1</v>
@@ -477,7 +477,7 @@
         <v>A2</v>
       </c>
       <c r="C3" t="str">
-        <v>DEMO-QS7-2026-00002</v>
+        <v>DEV01262000000000102</v>
       </c>
       <c r="D3" t="str">
         <v>VIH-1</v>
@@ -652,7 +652,7 @@
         <v>A7</v>
       </c>
       <c r="C8" t="str">
-        <v>DEMO-QS7-2026-00005</v>
+        <v>DEV01262000000000105</v>
       </c>
       <c r="D8" t="str">
         <v>VIH-1</v>
